--- a/artfynd/A 37143-2024 artfynd.xlsx
+++ b/artfynd/A 37143-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117148408</v>
+        <v>117148429</v>
       </c>
       <c r="B2" t="n">
-        <v>56199</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -799,22 +794,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Brüsin, Isabella Honnér</t>
+          <t>Martin Brüsin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117148429</v>
+        <v>117148454</v>
       </c>
       <c r="B3" t="n">
-        <v>56194</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,26 +812,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -937,42 +927,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117148386</v>
+        <v>117148401</v>
       </c>
       <c r="B4" t="n">
-        <v>56201</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1071,12 +1056,7 @@
         <v>117148470</v>
       </c>
       <c r="B5" t="n">
-        <v>56180</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1199,42 +1179,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117148454</v>
+        <v>117148386</v>
       </c>
       <c r="B6" t="n">
-        <v>56187</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205992</v>
+        <v>206002</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">

--- a/artfynd/A 37143-2024 artfynd.xlsx
+++ b/artfynd/A 37143-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117148429</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117148454</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117148401</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117148470</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1302,8 +1327,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117148386</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>